--- a/artfynd/A 3109-2020 artfynd.xlsx
+++ b/artfynd/A 3109-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3109-2020 artfynd.xlsx
+++ b/artfynd/A 3109-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,255 +1148,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>85969715</v>
-      </c>
-      <c r="B6" t="n">
-        <v>77713</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1642</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Långskägg</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Usnea longissima</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Åkälen, Flurkmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>754923.6661513925</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7106330.159698935</v>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2020-06-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2020-06-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Andreas Drott</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Andreas Drott</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>111046559</v>
-      </c>
-      <c r="B7" t="n">
-        <v>77722</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1642</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Långskägg</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Usnea longissima</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Långskäggets spår, Vb</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>754924.5863817577</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7106335.083959497</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Jag tror jag var i området minst 1h och letade, både i denna ände, i mitten och i andra änden. Hittade mot slutet girlangen på bild samt en till, båda nära Carls ursprungliga fynd, dvs mot gränsen till Skogsstyrelsens hygge och typ utanför reservatsgränsen? Kunde inte hitta något träd med ett "tiotal bålar", som Carl funnit. Funderade på om det trädet kan ha varit ett av de flera hänsynsträd som Skogsstyrelsen skonat men som nu hade vält. Ska förhoppningsvis dit och leta en gång till framöver. Fann någon annan småspännande usnea mitt i.</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
